--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98572</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92743</v>
+        <v>92748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,6 +1006,901 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128668179</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552097</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6842742</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växer på förmodad kolbotten. tillsammans med knärot.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128666699</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98579</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552076</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6842720</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ovanlig växtplats, helt intill bäcken, mycket fuktigt.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128670325</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552083</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6842727</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid förmodad kojruin.Tillsammans med knärot.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128668071</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98579</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552097</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6842742</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växtplatsen är en förmodad kolningsplats. Finns tyvärr inte inlagd på Fornsök. Knäroten växer tillsammans med och bland dropptaggsvamp.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128666421</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91231</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552050</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6842707</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Helt intill bäcken. Norra sidan.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carina Frost, Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128668365</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92776</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552105</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6842738</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128670372</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98579</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>552083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6842727</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Vid förmodad kojruin.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128669319</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98579</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långtjärnsbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>552105</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6842738</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer på förmodad kolbotten tillsammans med svart taggsvamp.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128666421</v>
       </c>
       <c r="B9" t="n">
-        <v>91231</v>
+        <v>91237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>128668365</v>
       </c>
       <c r="B10" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -1459,36 +1459,44 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128666421</v>
+        <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>91237</v>
+        <v>92782</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1497,13 +1505,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>552050</v>
+        <v>552105</v>
       </c>
       <c r="R9" t="n">
-        <v>6842707</v>
+        <v>6842738</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,11 +1541,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Helt intill bäcken. Norra sidan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,51 +1561,43 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128668365</v>
+        <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>92782</v>
+        <v>91237</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1611,13 +1606,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>552105</v>
+        <v>552050</v>
       </c>
       <c r="R10" t="n">
-        <v>6842738</v>
+        <v>6842707</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,6 +1642,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Helt intill bäcken. Norra sidan.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91237</v>
+        <v>91239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,21 +1472,12 @@
       <c r="E9" t="n">
         <v>5449</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>7</t>
@@ -1571,7 +1562,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1668,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,7 +1783,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 41867-2025 artfynd.xlsx
+++ b/artfynd/A 41867-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128633169</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128632620</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>128632785</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128668179</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>128666699</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>128670325</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128668071</v>
       </c>
       <c r="B8" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>128668365</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>128666421</v>
       </c>
       <c r="B10" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>128670372</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>128669319</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
